--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.30873753640678</v>
+        <v>4.762669849666102</v>
       </c>
       <c r="D2" t="n">
-        <v>28.45179724085269</v>
+        <v>4.623417051638563</v>
       </c>
       <c r="E2" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F2" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.01503194142828</v>
+        <v>1.627442690482096</v>
       </c>
       <c r="D3" t="n">
-        <v>11.25572950962157</v>
+        <v>1.829056045313505</v>
       </c>
       <c r="E3" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F3" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.29559791995401</v>
+        <v>1.835534661992526</v>
       </c>
       <c r="D4" t="n">
-        <v>12.82149852227971</v>
+        <v>2.083493509870453</v>
       </c>
       <c r="E4" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F4" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.44519647097741</v>
+        <v>2.347344426533828</v>
       </c>
       <c r="D5" t="n">
-        <v>13.21821415475566</v>
+        <v>2.147959800147794</v>
       </c>
       <c r="E5" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F5" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.56773158529229</v>
+        <v>4.317256382609997</v>
       </c>
       <c r="D6" t="n">
-        <v>27.4711621730627</v>
+        <v>4.464063853122688</v>
       </c>
       <c r="E6" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F6" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.447965998381449</v>
+        <v>1.535294474736985</v>
       </c>
       <c r="D7" t="n">
-        <v>8.616547141633403</v>
+        <v>1.400188910515428</v>
       </c>
       <c r="E7" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F7" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.51752806385923</v>
+        <v>3.171598310377125</v>
       </c>
       <c r="D8" t="n">
-        <v>20.14545449646907</v>
+        <v>3.273636355676224</v>
       </c>
       <c r="E8" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F8" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.38585202548155</v>
+        <v>2.825200954140753</v>
       </c>
       <c r="D9" t="n">
-        <v>17.65274670535083</v>
+        <v>2.86857133961951</v>
       </c>
       <c r="E9" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F9" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.06472101748485</v>
+        <v>3.585517165341289</v>
       </c>
       <c r="D10" t="n">
-        <v>20.84662989986985</v>
+        <v>3.387577358728851</v>
       </c>
       <c r="E10" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F10" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.12014324045078</v>
+        <v>2.782023276573252</v>
       </c>
       <c r="D11" t="n">
-        <v>15.14439722644438</v>
+        <v>2.460964549297212</v>
       </c>
       <c r="E11" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F11" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.43839459867032</v>
+        <v>3.321239122283927</v>
       </c>
       <c r="D12" t="n">
-        <v>19.37690186835307</v>
+        <v>3.148746553607375</v>
       </c>
       <c r="E12" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F12" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>16.56822243775078</v>
+        <v>2.692336146134501</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1116611485335</v>
+        <v>2.618144936636694</v>
       </c>
       <c r="E13" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F13" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>38.21356185042186</v>
+        <v>6.209703800693553</v>
       </c>
       <c r="D14" t="n">
-        <v>38.41846258439084</v>
+        <v>6.243000169963511</v>
       </c>
       <c r="E14" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F14" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.11850221990617</v>
+        <v>6.356756610734752</v>
       </c>
       <c r="D15" t="n">
-        <v>39.17173652771849</v>
+        <v>6.365407185754254</v>
       </c>
       <c r="E15" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F15" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>30.19505404739133</v>
+        <v>4.906696282701091</v>
       </c>
       <c r="D16" t="n">
-        <v>35.70453989908903</v>
+        <v>5.801987733601968</v>
       </c>
       <c r="E16" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F16" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>40.60987698445599</v>
+        <v>6.599105009974098</v>
       </c>
       <c r="D17" t="n">
-        <v>40.28393801383869</v>
+        <v>6.546139927248786</v>
       </c>
       <c r="E17" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F17" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>22.92393824028593</v>
+        <v>3.725139964046464</v>
       </c>
       <c r="D18" t="n">
-        <v>19.16943887113439</v>
+        <v>3.115033816559338</v>
       </c>
       <c r="E18" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F18" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>35.83145632713111</v>
+        <v>5.822611653158805</v>
       </c>
       <c r="D19" t="n">
-        <v>36.23333287938435</v>
+        <v>5.887916592899957</v>
       </c>
       <c r="E19" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F19" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>21.25223053626041</v>
+        <v>3.453487462142316</v>
       </c>
       <c r="D20" t="n">
-        <v>21.57331087351726</v>
+        <v>3.505663016946555</v>
       </c>
       <c r="E20" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F20" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>16.7021550767538</v>
+        <v>2.714100199972493</v>
       </c>
       <c r="D21" t="n">
-        <v>16.85967712717723</v>
+        <v>2.7396975331663</v>
       </c>
       <c r="E21" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F21" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>22.70277530375388</v>
+        <v>3.689200986860006</v>
       </c>
       <c r="D22" t="n">
-        <v>22.42164074552987</v>
+        <v>3.643516621148605</v>
       </c>
       <c r="E22" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F22" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>39.00615058053979</v>
+        <v>6.338499469337716</v>
       </c>
       <c r="D23" t="n">
-        <v>38.60270010772627</v>
+        <v>6.272938767505519</v>
       </c>
       <c r="E23" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F23" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>32.14845770742471</v>
+        <v>5.224124377456516</v>
       </c>
       <c r="D24" t="n">
-        <v>31.7502039946803</v>
+        <v>5.159408149135548</v>
       </c>
       <c r="E24" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F24" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>39.3298265275438</v>
+        <v>6.391096810725868</v>
       </c>
       <c r="D25" t="n">
-        <v>38.9886922908645</v>
+        <v>6.335662497265481</v>
       </c>
       <c r="E25" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F25" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>26.92929840817282</v>
+        <v>4.376010991328083</v>
       </c>
       <c r="D26" t="n">
-        <v>26.63779876626513</v>
+        <v>4.328642299518084</v>
       </c>
       <c r="E26" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F26" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>37.93356416952656</v>
+        <v>6.164204177548067</v>
       </c>
       <c r="D27" t="n">
-        <v>37.6531840057135</v>
+        <v>6.118642400928444</v>
       </c>
       <c r="E27" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F27" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>26.47888210351145</v>
+        <v>4.30281834182061</v>
       </c>
       <c r="D28" t="n">
-        <v>26.19295997308912</v>
+        <v>4.256355995626983</v>
       </c>
       <c r="E28" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F28" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>37.02072650117256</v>
+        <v>6.015868056440541</v>
       </c>
       <c r="D29" t="n">
-        <v>36.87287213620225</v>
+        <v>5.991841722132865</v>
       </c>
       <c r="E29" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F29" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>11.87622212961123</v>
+        <v>1.929886096061824</v>
       </c>
       <c r="D30" t="n">
-        <v>11.85654217859824</v>
+        <v>1.926688104022215</v>
       </c>
       <c r="E30" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F30" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>29.99953775026894</v>
+        <v>4.874924884418703</v>
       </c>
       <c r="D31" t="n">
-        <v>29.96232501260721</v>
+        <v>4.868877814548672</v>
       </c>
       <c r="E31" t="n">
-        <v>9.753728436384096</v>
+        <v>1.584980870912416</v>
       </c>
       <c r="F31" t="n">
-        <v>9.941136609115828</v>
+        <v>1.615434698981322</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
